--- a/input/sales.xlsx
+++ b/input/sales.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\python_study\sqlite_app\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{396B9E29-C92F-4D77-969E-C291848EC406}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13DA600D-6743-4ED9-8FB9-33D408CDF2C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="21">
   <si>
     <t>date</t>
   </si>
@@ -58,6 +58,70 @@
   </si>
   <si>
     <t>バナナ</t>
+  </si>
+  <si>
+    <t>大阪店</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>博多店</t>
+    <rPh sb="0" eb="3">
+      <t>ハカタテン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>北京店</t>
+    <rPh sb="0" eb="2">
+      <t>ペキン</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>テン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>野菜</t>
+    <rPh sb="0" eb="2">
+      <t>ヤサイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>白菜</t>
+    <rPh sb="0" eb="2">
+      <t>ハクサイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>マグロ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>魚</t>
+    <rPh sb="0" eb="1">
+      <t>サカナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>玉ねぎ</t>
+    <rPh sb="0" eb="1">
+      <t>タマ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ハチミツ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>その他</t>
+    <rPh sb="2" eb="3">
+      <t>タ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -383,7 +447,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="16.19921875" customWidth="1"/>
@@ -457,6 +521,74 @@
         <v>120</v>
       </c>
     </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="1">
+        <v>46114</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="1">
+        <v>46116</v>
+      </c>
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="1">
+        <v>46116</v>
+      </c>
+      <c r="B7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="1">
+        <v>46117</v>
+      </c>
+      <c r="B8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8">
+        <v>900</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
